--- a/data/trans_orig/P1408-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1408-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2007</t>
+          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18441</t>
+          <t>17651</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5797</t>
+          <t>5687</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18797</t>
+          <t>18926</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>254569</t>
+          <t>255359</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267984</t>
+          <t>267942</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>255686</t>
+          <t>256149</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>515051</t>
+          <t>514922</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>528051</t>
+          <t>528161</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15304</t>
+          <t>15720</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35846</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10949</t>
+          <t>11761</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27634</t>
+          <t>28545</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30941</t>
+          <t>32205</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57639</t>
+          <t>57160</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>457229</t>
+          <t>454870</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>477771</t>
+          <t>477355</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>476315</t>
+          <t>475404</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>493000</t>
+          <t>492188</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>939385</t>
+          <t>939864</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>966083</t>
+          <t>964819</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6703</t>
+          <t>7431</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21359</t>
+          <t>22081</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>8198</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9540</t>
+          <t>9460</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25655</t>
+          <t>24839</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>297487</t>
+          <t>296765</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>312143</t>
+          <t>311415</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>326172</t>
+          <t>327214</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>628603</t>
+          <t>629419</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>644718</t>
+          <t>644798</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8971</t>
+          <t>9234</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24372</t>
+          <t>23612</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2253</t>
+          <t>2807</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13519</t>
+          <t>13140</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14089</t>
+          <t>13531</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32104</t>
+          <t>31609</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>334299</t>
+          <t>335059</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>349700</t>
+          <t>349437</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>357937</t>
+          <t>358316</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>369203</t>
+          <t>368649</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>698023</t>
+          <t>698518</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>716038</t>
+          <t>716596</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14700</t>
+          <t>15676</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3908</t>
+          <t>4113</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16030</t>
+          <t>16209</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10960</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26787</t>
+          <t>26937</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>188608</t>
+          <t>187632</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>199427</t>
+          <t>199248</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>191638</t>
+          <t>191459</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203760</t>
+          <t>203555</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>384189</t>
+          <t>384039</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>400016</t>
+          <t>400228</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12017</t>
+          <t>11595</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9020</t>
+          <t>9254</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4674</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17167</t>
+          <t>15806</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258794</t>
+          <t>259216</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268790</t>
+          <t>268867</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>269124</t>
+          <t>268890</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277113</t>
+          <t>277116</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>531788</t>
+          <t>533149</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>544281</t>
+          <t>544753</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18706</t>
+          <t>18275</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38271</t>
+          <t>38049</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13483</t>
+          <t>13055</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30639</t>
+          <t>31200</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36459</t>
+          <t>37740</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63531</t>
+          <t>64690</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>576756</t>
+          <t>576978</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>596321</t>
+          <t>596752</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>607580</t>
+          <t>607019</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>624736</t>
+          <t>625164</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1189715</t>
+          <t>1188556</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1216787</t>
+          <t>1215506</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22794</t>
+          <t>21978</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44380</t>
+          <t>44206</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19334</t>
+          <t>19287</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>40626</t>
+          <t>40272</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>47041</t>
+          <t>47720</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>78856</t>
+          <t>80360</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>699415</t>
+          <t>699589</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>721001</t>
+          <t>721817</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>742885</t>
+          <t>743239</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>764177</t>
+          <t>764224</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1448450</t>
+          <t>1446946</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1480265</t>
+          <t>1479586</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>115329</t>
+          <t>113437</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>158816</t>
+          <t>157978</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>74983</t>
+          <t>73793</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>111032</t>
+          <t>112672</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>200369</t>
+          <t>198466</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>258465</t>
+          <t>259841</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3117727</t>
+          <t>3118565</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3161214</t>
+          <t>3163106</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3268165</t>
+          <t>3266525</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3304214</t>
+          <t>3305404</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6397276</t>
+          <t>6395900</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6455372</t>
+          <t>6457275</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2012</t>
+          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>959</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9605</t>
+          <t>9592</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12286</t>
+          <t>12023</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15210</t>
+          <t>16121</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>285133</t>
+          <t>285146</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293767</t>
+          <t>293779</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274959</t>
+          <t>275222</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286193</t>
+          <t>286217</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>566773</t>
+          <t>565862</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>578963</t>
+          <t>578785</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10042</t>
+          <t>9379</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27867</t>
+          <t>27561</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2952</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12913</t>
+          <t>12777</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14674</t>
+          <t>13641</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35099</t>
+          <t>34224</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>477660</t>
+          <t>477966</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>495485</t>
+          <t>496148</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>510852</t>
+          <t>510988</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>520813</t>
+          <t>521561</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>994193</t>
+          <t>995068</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1014618</t>
+          <t>1015651</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>3334</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14379</t>
+          <t>15121</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10677</t>
+          <t>11314</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6610</t>
+          <t>6661</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21334</t>
+          <t>21515</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>309667</t>
+          <t>308925</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>320929</t>
+          <t>320712</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>330343</t>
+          <t>329706</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>339029</t>
+          <t>339082</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>643732</t>
+          <t>643551</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>658456</t>
+          <t>658405</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5395</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20354</t>
+          <t>21844</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5193</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18238</t>
+          <t>17950</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13218</t>
+          <t>12508</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32172</t>
+          <t>33238</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>353628</t>
+          <t>352138</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>368587</t>
+          <t>368574</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>370713</t>
+          <t>371001</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>383758</t>
+          <t>383950</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>730761</t>
+          <t>729695</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>749715</t>
+          <t>750425</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8820</t>
+          <t>10773</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9953</t>
+          <t>10725</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>203798</t>
+          <t>201845</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>211592</t>
+          <t>211578</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>214337</t>
+          <t>214799</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>422256</t>
+          <t>421484</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>431104</t>
+          <t>431103</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>6370</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22176</t>
+          <t>22273</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>944</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9335</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26321</t>
+          <t>26006</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>251805</t>
+          <t>251708</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>267616</t>
+          <t>267611</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277151</t>
+          <t>277152</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>525756</t>
+          <t>526071</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>542742</t>
+          <t>543744</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14370</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3112</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14547</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23514</t>
+          <t>23368</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>648418</t>
+          <t>648559</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>659632</t>
+          <t>659745</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>679306</t>
+          <t>678966</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>690741</t>
+          <t>690630</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1333127</t>
+          <t>1333273</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1348318</t>
+          <t>1348530</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23698</t>
+          <t>23020</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10904</t>
+          <t>12192</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9839</t>
+          <t>9836</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29935</t>
+          <t>29448</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>755400</t>
+          <t>756078</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>772824</t>
+          <t>772607</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>810491</t>
+          <t>809203</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>819352</t>
+          <t>819304</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1570558</t>
+          <t>1571045</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1590654</t>
+          <t>1590657</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>58749</t>
+          <t>56944</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>96904</t>
+          <t>93437</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>31756</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>58750</t>
+          <t>58506</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>94290</t>
+          <t>95569</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>140732</t>
+          <t>139176</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3329875</t>
+          <t>3333342</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3368030</t>
+          <t>3369835</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3495166</t>
+          <t>3495410</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3523007</t>
+          <t>3522160</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6839962</t>
+          <t>6841518</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6886404</t>
+          <t>6885125</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2016</t>
+          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3199</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14801</t>
+          <t>16538</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6247</t>
+          <t>6212</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4235</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17524</t>
+          <t>18028</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>278960</t>
+          <t>277223</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>290671</t>
+          <t>290562</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>282456</t>
+          <t>282491</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>564940</t>
+          <t>564436</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>578229</t>
+          <t>578643</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7554</t>
+          <t>7314</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21913</t>
+          <t>22235</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15591</t>
+          <t>14270</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13153</t>
+          <t>12940</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31915</t>
+          <t>31526</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>480662</t>
+          <t>480340</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>495021</t>
+          <t>495261</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>507493</t>
+          <t>508814</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>519721</t>
+          <t>519771</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>993744</t>
+          <t>994133</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1012506</t>
+          <t>1012719</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1484</t>
+          <t>1583</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9255</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9492</t>
+          <t>9144</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3518</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14882</t>
+          <t>14793</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>309310</t>
+          <t>308620</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317081</t>
+          <t>316982</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>326817</t>
+          <t>327165</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>335256</t>
+          <t>335269</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>639992</t>
+          <t>640081</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>651303</t>
+          <t>651356</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4713</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16389</t>
+          <t>16748</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11404</t>
+          <t>11788</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8280</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23410</t>
+          <t>23736</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>353575</t>
+          <t>353216</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>365251</t>
+          <t>365191</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>375879</t>
+          <t>375495</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>385310</t>
+          <t>385370</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>733837</t>
+          <t>733511</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>748967</t>
+          <t>748378</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1766</t>
+          <t>1644</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10096</t>
+          <t>10459</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6889</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12746</t>
+          <t>13326</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>201125</t>
+          <t>200762</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209455</t>
+          <t>209577</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>211698</t>
+          <t>211712</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>417062</t>
+          <t>416482</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>978</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>8844</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11098</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16097</t>
+          <t>15888</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253520</t>
+          <t>254279</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262132</t>
+          <t>262145</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>262017</t>
+          <t>262936</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>271912</t>
+          <t>271876</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>520141</t>
+          <t>520350</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>532353</t>
+          <t>532289</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21772</t>
+          <t>19829</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4985</t>
+          <t>5095</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19866</t>
+          <t>18592</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13514</t>
+          <t>13596</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34328</t>
+          <t>33648</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>634786</t>
+          <t>636729</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>650955</t>
+          <t>650868</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>671428</t>
+          <t>672702</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>686309</t>
+          <t>686199</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1313524</t>
+          <t>1314204</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1334338</t>
+          <t>1334256</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>6445</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20435</t>
+          <t>20461</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>5648</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19740</t>
+          <t>19963</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14275</t>
+          <t>14418</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>33932</t>
+          <t>33648</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>758148</t>
+          <t>758122</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>771975</t>
+          <t>772138</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>806427</t>
+          <t>806204</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>821218</t>
+          <t>820519</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1570818</t>
+          <t>1571102</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1590475</t>
+          <t>1590332</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>51511</t>
+          <t>51201</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>85453</t>
+          <t>83469</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>32981</t>
+          <t>33464</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>61614</t>
+          <t>60705</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>92245</t>
+          <t>91677</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>135720</t>
+          <t>132478</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3308897</t>
+          <t>3310881</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3342839</t>
+          <t>3343149</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3482928</t>
+          <t>3483837</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3511561</t>
+          <t>3511078</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6803172</t>
+          <t>6806414</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6846647</t>
+          <t>6847215</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2023</t>
+          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>7593</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12791</t>
+          <t>13465</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>303254</t>
+          <t>302933</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309929</t>
+          <t>310048</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>282329</t>
+          <t>282042</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>287776</t>
+          <t>287703</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>588286</t>
+          <t>587612</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>596734</t>
+          <t>596462</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5507</t>
+          <t>5364</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17383</t>
+          <t>18130</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5524</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16217</t>
+          <t>17721</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13535</t>
+          <t>12773</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28682</t>
+          <t>29501</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>500010</t>
+          <t>499263</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>511886</t>
+          <t>512029</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>496441</t>
+          <t>494937</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>507134</t>
+          <t>507145</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1001369</t>
+          <t>1000550</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1016516</t>
+          <t>1017278</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>5923</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16816</t>
+          <t>17343</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7220</t>
+          <t>7223</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16549</t>
+          <t>16717</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15394</t>
+          <t>14984</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29180</t>
+          <t>28841</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>299234</t>
+          <t>298707</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310207</t>
+          <t>310127</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>332579</t>
+          <t>332411</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>341908</t>
+          <t>341905</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>635998</t>
+          <t>636337</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>649784</t>
+          <t>650194</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7039</t>
+          <t>7346</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22548</t>
+          <t>22011</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6880</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26111</t>
+          <t>24887</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16096</t>
+          <t>16855</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41100</t>
+          <t>39818</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>290009</t>
+          <t>290546</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>305518</t>
+          <t>305211</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>449607</t>
+          <t>450831</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>468838</t>
+          <t>468728</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>747174</t>
+          <t>748456</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>772178</t>
+          <t>771419</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6893</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>1581</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5892</t>
+          <t>6217</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11230</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>171849</t>
+          <t>171192</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177532</t>
+          <t>177249</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>201983</t>
+          <t>201658</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206288</t>
+          <t>206294</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>375387</t>
+          <t>375378</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>382690</t>
+          <t>382565</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18165</t>
+          <t>18723</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6141</t>
+          <t>6073</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14448</t>
+          <t>14460</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16107</t>
+          <t>16277</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29668</t>
+          <t>29830</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>251471</t>
+          <t>250913</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261503</t>
+          <t>261493</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>241939</t>
+          <t>241927</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>250246</t>
+          <t>250314</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>496355</t>
+          <t>496193</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>509916</t>
+          <t>509746</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10601</t>
+          <t>10715</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26945</t>
+          <t>26442</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>10090</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35500</t>
+          <t>35415</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24095</t>
+          <t>21332</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55206</t>
+          <t>52126</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>595540</t>
+          <t>596043</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>611884</t>
+          <t>611770</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>812182</t>
+          <t>812267</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>837648</t>
+          <t>837592</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1414961</t>
+          <t>1418041</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1446072</t>
+          <t>1448835</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5515</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22642</t>
+          <t>23339</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10921</t>
+          <t>10831</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23170</t>
+          <t>22716</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17188</t>
+          <t>18386</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>40547</t>
+          <t>42340</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>906078</t>
+          <t>905381</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>923205</t>
+          <t>923844</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>692222</t>
+          <t>692676</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>704471</t>
+          <t>704561</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1603565</t>
+          <t>1601772</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1626924</t>
+          <t>1625726</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>63471</t>
+          <t>62876</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>102715</t>
+          <t>101720</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,82 +13461,82 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>88570</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>70208</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>108383</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
           <t>2,97%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>88570</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>71014</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>107790</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>172262</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>144396</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>201656</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
         <is>
           <t>2,42%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>172262</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>147277</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>200879</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3354311</t>
+          <t>3355306</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3393555</t>
+          <t>3394150</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,82 +13574,82 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>97,06%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>98,18%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>5198</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>3565904</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>3546091</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3584266</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>97,58%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
           <t>97,03%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>98,16%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>5198</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>3565904</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>3546684</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>3583460</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>98,08%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>8454</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>6939237</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>6909843</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>6967103</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
         <is>
           <t>97,58%</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>97,05%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>98,06%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>8454</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>6939237</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>6910620</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>6964222</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>97,58%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1408-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1408-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17651</t>
+          <t>17436</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>5140</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5687</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18926</t>
+          <t>18884</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>255359</t>
+          <t>255574</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267942</t>
+          <t>267868</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>256149</t>
+          <t>255698</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>514922</t>
+          <t>514964</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>528161</t>
+          <t>528560</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15720</t>
+          <t>15942</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>11664</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28545</t>
+          <t>28658</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32205</t>
+          <t>31362</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57160</t>
+          <t>58829</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>454870</t>
+          <t>456490</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>477355</t>
+          <t>477133</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>475404</t>
+          <t>475291</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>492188</t>
+          <t>492285</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>939864</t>
+          <t>938195</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>964819</t>
+          <t>965662</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>7232</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22081</t>
+          <t>22901</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>923</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8198</t>
+          <t>8673</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9460</t>
+          <t>9611</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24839</t>
+          <t>25952</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>296765</t>
+          <t>295945</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>311415</t>
+          <t>311614</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>327214</t>
+          <t>326739</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>334486</t>
+          <t>334489</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>629419</t>
+          <t>628306</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>644798</t>
+          <t>644647</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9234</t>
+          <t>8924</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23612</t>
+          <t>23932</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>2251</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13140</t>
+          <t>13113</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13531</t>
+          <t>14104</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31609</t>
+          <t>31984</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>335059</t>
+          <t>334739</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>349437</t>
+          <t>349747</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>358316</t>
+          <t>358343</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>368649</t>
+          <t>369205</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>698518</t>
+          <t>698143</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>716596</t>
+          <t>716023</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>3974</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15676</t>
+          <t>15837</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>3928</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16209</t>
+          <t>17475</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10748</t>
+          <t>10795</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26937</t>
+          <t>26881</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>187632</t>
+          <t>187471</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>199248</t>
+          <t>199334</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>191459</t>
+          <t>190193</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203555</t>
+          <t>203740</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>384039</t>
+          <t>384095</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>400228</t>
+          <t>400181</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>11753</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9254</t>
+          <t>8920</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15806</t>
+          <t>17058</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259216</t>
+          <t>259058</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268867</t>
+          <t>268833</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>268890</t>
+          <t>269224</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277116</t>
+          <t>277110</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>533149</t>
+          <t>531897</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>544753</t>
+          <t>544828</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18275</t>
+          <t>18690</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38049</t>
+          <t>38822</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13055</t>
+          <t>13446</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31200</t>
+          <t>32267</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>37740</t>
+          <t>36249</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>64690</t>
+          <t>63402</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>576978</t>
+          <t>576205</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>596752</t>
+          <t>596337</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>607019</t>
+          <t>605952</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>625164</t>
+          <t>624773</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1188556</t>
+          <t>1189844</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1215506</t>
+          <t>1216997</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,11%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21978</t>
+          <t>22889</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44206</t>
+          <t>44304</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19287</t>
+          <t>19446</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>40272</t>
+          <t>42204</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>47720</t>
+          <t>47632</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>80360</t>
+          <t>78162</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>699589</t>
+          <t>699491</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>721817</t>
+          <t>720906</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>743239</t>
+          <t>741307</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>764224</t>
+          <t>764065</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1446946</t>
+          <t>1449144</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1479586</t>
+          <t>1479674</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>113437</t>
+          <t>116127</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>157978</t>
+          <t>161980</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>73793</t>
+          <t>74356</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>112672</t>
+          <t>110814</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>198466</t>
+          <t>199435</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>259841</t>
+          <t>257911</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3118565</t>
+          <t>3114563</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3163106</t>
+          <t>3160416</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3266525</t>
+          <t>3268383</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3305404</t>
+          <t>3304841</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6395900</t>
+          <t>6397830</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6457275</t>
+          <t>6456306</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>949</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9592</t>
+          <t>8838</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12023</t>
+          <t>11994</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16121</t>
+          <t>15920</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>285146</t>
+          <t>285900</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293779</t>
+          <t>293789</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>275222</t>
+          <t>275251</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286217</t>
+          <t>286202</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>565862</t>
+          <t>566063</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>578785</t>
+          <t>578891</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9379</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27561</t>
+          <t>27788</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12777</t>
+          <t>12146</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13641</t>
+          <t>14404</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34224</t>
+          <t>34076</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>477966</t>
+          <t>477739</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>496148</t>
+          <t>495328</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>510988</t>
+          <t>511619</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>521561</t>
+          <t>521603</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>995068</t>
+          <t>995216</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1015651</t>
+          <t>1014888</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15121</t>
+          <t>15204</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11314</t>
+          <t>11592</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6661</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21515</t>
+          <t>23201</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308925</t>
+          <t>308842</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>320712</t>
+          <t>320921</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>329706</t>
+          <t>329428</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>339082</t>
+          <t>338972</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>643551</t>
+          <t>641865</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>658405</t>
+          <t>657961</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>5204</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21844</t>
+          <t>20654</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>4949</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17950</t>
+          <t>18329</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12508</t>
+          <t>12915</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33238</t>
+          <t>31241</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>352138</t>
+          <t>353328</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>368574</t>
+          <t>368778</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>371001</t>
+          <t>370622</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>383950</t>
+          <t>384002</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>729695</t>
+          <t>731692</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>750425</t>
+          <t>750018</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10773</t>
+          <t>8760</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4792</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10725</t>
+          <t>9695</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>201845</t>
+          <t>203858</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>211578</t>
+          <t>211607</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>214799</t>
+          <t>213390</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>421484</t>
+          <t>422514</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>431103</t>
+          <t>431116</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>6390</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22273</t>
+          <t>22432</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>948</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7970</t>
+          <t>8383</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>8939</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26006</t>
+          <t>25200</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>251708</t>
+          <t>251549</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>267611</t>
+          <t>267591</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>270126</t>
+          <t>269713</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277152</t>
+          <t>277148</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>526071</t>
+          <t>526877</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>543744</t>
+          <t>543138</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14229</t>
+          <t>13439</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>3284</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14223</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>8502</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23368</t>
+          <t>24543</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>648559</t>
+          <t>649349</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>659745</t>
+          <t>659763</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>678966</t>
+          <t>679630</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>690630</t>
+          <t>690569</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1333273</t>
+          <t>1332098</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1348530</t>
+          <t>1348139</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>5656</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23020</t>
+          <t>22413</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12192</t>
+          <t>11968</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>10828</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29448</t>
+          <t>28733</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>756078</t>
+          <t>756685</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>772607</t>
+          <t>773442</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>809203</t>
+          <t>809427</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>819304</t>
+          <t>819314</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1571045</t>
+          <t>1571760</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1590657</t>
+          <t>1589665</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>56944</t>
+          <t>55218</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>93437</t>
+          <t>91308</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,74 +6815,74 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>42468</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>30856</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>57667</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>116121</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>95606</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>141689</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
           <t>1,66%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>42468</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>31756</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>58506</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>116121</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>95569</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>139176</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
           <t>1,37%</t>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3333342</t>
+          <t>3335471</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3369835</t>
+          <t>3371561</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,77 +6928,77 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>3255</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>3511448</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>3496249</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3523060</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>98,81%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>98,38%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>99,13%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>6398</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>6864573</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>6839005</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>6885088</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
           <t>98,34%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>3255</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>3511448</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>3495410</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>3522160</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>98,35%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>6398</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>6864573</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>6841518</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>6885125</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>98,34%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3199</t>
+          <t>2818</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16538</t>
+          <t>15554</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6212</t>
+          <t>6311</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18028</t>
+          <t>18364</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>277223</t>
+          <t>278207</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>290562</t>
+          <t>290943</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>282491</t>
+          <t>282392</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>564436</t>
+          <t>564100</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>578643</t>
+          <t>578379</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>7289</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22235</t>
+          <t>21588</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14270</t>
+          <t>15438</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12940</t>
+          <t>13698</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31526</t>
+          <t>32175</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>480340</t>
+          <t>480987</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>495261</t>
+          <t>495286</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>508814</t>
+          <t>507646</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>519771</t>
+          <t>519782</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>994133</t>
+          <t>993484</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1012719</t>
+          <t>1011961</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1583</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>9440</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9144</t>
+          <t>9212</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14793</t>
+          <t>14827</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308620</t>
+          <t>309125</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316982</t>
+          <t>317090</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>327165</t>
+          <t>327097</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>640081</t>
+          <t>640047</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>651356</t>
+          <t>651374</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4773</t>
+          <t>4795</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16748</t>
+          <t>17303</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11788</t>
+          <t>12373</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>8649</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23736</t>
+          <t>23400</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>353216</t>
+          <t>352661</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>365191</t>
+          <t>365169</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>375495</t>
+          <t>374910</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>385370</t>
+          <t>385292</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>733511</t>
+          <t>733847</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>748378</t>
+          <t>748598</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1644</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10459</t>
+          <t>10294</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>6972</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2863</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13326</t>
+          <t>12463</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>200762</t>
+          <t>200927</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209577</t>
+          <t>209421</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>211712</t>
+          <t>211615</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>416482</t>
+          <t>417345</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>426945</t>
+          <t>426838</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>999</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8844</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10351</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>3934</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15888</t>
+          <t>16105</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254279</t>
+          <t>253652</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262145</t>
+          <t>262124</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>262936</t>
+          <t>262764</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>271876</t>
+          <t>271947</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>520350</t>
+          <t>520133</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>532289</t>
+          <t>532304</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>5748</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19829</t>
+          <t>20854</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18592</t>
+          <t>19101</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13596</t>
+          <t>13407</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33648</t>
+          <t>33706</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>636729</t>
+          <t>635704</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>650868</t>
+          <t>650810</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>672702</t>
+          <t>672193</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>686199</t>
+          <t>686051</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1314204</t>
+          <t>1314146</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1334256</t>
+          <t>1334445</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6445</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20461</t>
+          <t>21334</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5648</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19963</t>
+          <t>19499</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14418</t>
+          <t>14808</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>33648</t>
+          <t>32913</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>758122</t>
+          <t>757249</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>772138</t>
+          <t>771334</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>806204</t>
+          <t>806668</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>820519</t>
+          <t>821079</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1571102</t>
+          <t>1571837</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1590332</t>
+          <t>1589942</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>51201</t>
+          <t>51915</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>83469</t>
+          <t>84355</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>33464</t>
+          <t>31237</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>60705</t>
+          <t>60482</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>91677</t>
+          <t>92622</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>132478</t>
+          <t>132714</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3310881</t>
+          <t>3309995</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3343149</t>
+          <t>3342435</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3483837</t>
+          <t>3484060</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3511078</t>
+          <t>3513305</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6806414</t>
+          <t>6806178</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6847215</t>
+          <t>6846270</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8510</t>
+          <t>9421</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7593</t>
+          <t>7449</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7838</t>
+          <t>8513</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4615</t>
+          <t>4840</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13465</t>
+          <t>14610</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>307532</t>
+          <t>314209</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>302933</t>
+          <t>309424</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>310048</t>
+          <t>317291</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>285708</t>
+          <t>312184</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>282042</t>
+          <t>308612</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>287703</t>
+          <t>314203</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>593239</t>
+          <t>626393</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>587612</t>
+          <t>620296</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>596462</t>
+          <t>630066</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,102 +11040,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>10511</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5364</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18130</t>
+          <t>18431</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,48%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>10385</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>5792</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>16665</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,06%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>20896</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>13038</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>31058</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>1,95%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9707</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>5513</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>17721</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>19810</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>12773</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>29501</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -11153,102 +11153,102 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>507289</t>
+          <t>519149</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>499263</t>
+          <t>511229</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>512029</t>
+          <t>524262</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>98,02%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,52%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,98%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>533709</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>527429</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>538302</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>98,09%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,94%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>98,94%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1068</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1052858</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>1042696</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1060716</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t>98,05%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,5%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>502951</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>494937</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>507145</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>96,54%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>98,92%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1068</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1010241</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1000550</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1017278</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>98,08%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512658</t>
+          <t>544094</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512658</t>
+          <t>544094</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512658</t>
+          <t>544094</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1030051</t>
+          <t>1073754</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1030051</t>
+          <t>1073754</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1030051</t>
+          <t>1073754</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10260</t>
+          <t>10160</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17343</t>
+          <t>16255</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11187</t>
+          <t>11446</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16717</t>
+          <t>17381</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>21448</t>
+          <t>21606</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14984</t>
+          <t>15165</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28841</t>
+          <t>28839</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>305790</t>
+          <t>305833</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>298707</t>
+          <t>299738</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310127</t>
+          <t>310039</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>337941</t>
+          <t>344935</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>332411</t>
+          <t>339000</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>341905</t>
+          <t>349136</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>643730</t>
+          <t>650769</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>636337</t>
+          <t>643536</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>650194</t>
+          <t>657210</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12762</t>
+          <t>14345</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7346</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22011</t>
+          <t>24681</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13046</t>
+          <t>13979</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>8503</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24887</t>
+          <t>27757</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>25808</t>
+          <t>28323</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16855</t>
+          <t>18796</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39818</t>
+          <t>43418</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>299795</t>
+          <t>358800</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>290546</t>
+          <t>348464</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>305211</t>
+          <t>365165</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>462672</t>
+          <t>407982</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>450831</t>
+          <t>394204</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>468728</t>
+          <t>413458</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>762466</t>
+          <t>766784</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>748456</t>
+          <t>751689</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>771419</t>
+          <t>776311</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,67 +12069,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>3710</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1559</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7996</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>3499</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1493</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7550</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,22%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3369</t>
-        </is>
-      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1581</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6868</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>4332</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11239</t>
+          <t>11941</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>175243</t>
+          <t>201955</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>171192</t>
+          <t>197669</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177249</t>
+          <t>204106</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>204506</t>
+          <t>222924</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>201658</t>
+          <t>219932</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206294</t>
+          <t>224830</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>379749</t>
+          <t>424878</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>375378</t>
+          <t>420146</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>382565</t>
+          <t>427755</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>207875</t>
+          <t>226423</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207875</t>
+          <t>226423</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>207875</t>
+          <t>226423</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>386617</t>
+          <t>432087</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386617</t>
+          <t>432087</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>386617</t>
+          <t>432087</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12327</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>7621</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18723</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9383</t>
+          <t>9468</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6073</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14460</t>
+          <t>14283</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>21876</t>
+          <t>21794</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16277</t>
+          <t>16635</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29830</t>
+          <t>30151</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>257143</t>
+          <t>258380</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>250913</t>
+          <t>253141</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261493</t>
+          <t>263086</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>247004</t>
+          <t>253631</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>241927</t>
+          <t>248816</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>250314</t>
+          <t>257004</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>504147</t>
+          <t>512012</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>496193</t>
+          <t>503655</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>509746</t>
+          <t>517171</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>17048</t>
+          <t>18579</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10715</t>
+          <t>11323</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26442</t>
+          <t>28399</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>21970</t>
+          <t>24875</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10090</t>
+          <t>16462</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35415</t>
+          <t>36053</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>39018</t>
+          <t>43454</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21332</t>
+          <t>33265</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52126</t>
+          <t>61771</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>605437</t>
+          <t>699142</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>596043</t>
+          <t>689322</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>611770</t>
+          <t>706398</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>825712</t>
+          <t>744394</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>812267</t>
+          <t>733216</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>837592</t>
+          <t>752807</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1431149</t>
+          <t>1443536</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1418041</t>
+          <t>1425219</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1448835</t>
+          <t>1453725</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>622485</t>
+          <t>717721</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>622485</t>
+          <t>717721</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>622485</t>
+          <t>717721</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>847682</t>
+          <t>769269</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>847682</t>
+          <t>769269</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>847682</t>
+          <t>769269</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1470167</t>
+          <t>1486990</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1470167</t>
+          <t>1486990</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1470167</t>
+          <t>1486990</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>13615</t>
+          <t>15727</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4876</t>
+          <t>9777</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23339</t>
+          <t>23948</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>15980</t>
+          <t>18291</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10831</t>
+          <t>11739</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22716</t>
+          <t>25890</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>29595</t>
+          <t>34018</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18386</t>
+          <t>24928</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>42340</t>
+          <t>44634</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>915105</t>
+          <t>782345</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>905381</t>
+          <t>774124</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>923844</t>
+          <t>788295</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>699412</t>
+          <t>812318</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>692676</t>
+          <t>804719</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>704561</t>
+          <t>818870</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1614517</t>
+          <t>1594663</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1601772</t>
+          <t>1584047</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1625726</t>
+          <t>1603753</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>83692</t>
+          <t>89995</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>62876</t>
+          <t>72487</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>101720</t>
+          <t>107672</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>88570</t>
+          <t>95820</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>70208</t>
+          <t>81023</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>108383</t>
+          <t>113973</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>172262</t>
+          <t>185815</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>144396</t>
+          <t>159961</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>201656</t>
+          <t>211854</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3373334</t>
+          <t>3439813</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3355306</t>
+          <t>3422136</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3394150</t>
+          <t>3457321</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3565904</t>
+          <t>3632077</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3546091</t>
+          <t>3613924</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3584266</t>
+          <t>3646874</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6939237</t>
+          <t>7071891</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6909843</t>
+          <t>7045852</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6967103</t>
+          <t>7097745</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3457026</t>
+          <t>3529808</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3457026</t>
+          <t>3529808</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3457026</t>
+          <t>3529808</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3654474</t>
+          <t>3727897</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3654474</t>
+          <t>3727897</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3654474</t>
+          <t>3727897</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7111499</t>
+          <t>7257706</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7111499</t>
+          <t>7257706</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7111499</t>
+          <t>7257706</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
